--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.4863,0.3124,0.0960,0.0766</t>
-  </si>
-  <si>
-    <t>0.8218,0.0844,0.0250,0.0364</t>
-  </si>
-  <si>
-    <t>0.6049,0.2624,0.0944,0.0717</t>
-  </si>
-  <si>
-    <t>0.6916,0.1829,0.0589,0.0398</t>
-  </si>
-  <si>
-    <t>0.5622,0.3953,0.0557,0.0195</t>
-  </si>
-  <si>
-    <t>0.5540,0.4290,0.0748,0.0196</t>
-  </si>
-  <si>
-    <t>0.4653,0.4764,0.0883,0.0230</t>
-  </si>
-  <si>
-    <t>0.6056,0.3945,0.0300,0.0129</t>
-  </si>
-  <si>
-    <t>0.1444,0.7940,0.1722,0.0263</t>
-  </si>
-  <si>
-    <t>0.3080,0.6330,0.0668,0.0200</t>
-  </si>
-  <si>
-    <t>0.2610,0.7485,0.0701,0.0098</t>
-  </si>
-  <si>
-    <t>0.6139,0.3228,0.0177,0.0147</t>
-  </si>
-  <si>
-    <t>0.5163,0.2583,0.1573,0.0984</t>
-  </si>
-  <si>
-    <t>0.6581,0.2486,0.0758,0.0245</t>
-  </si>
-  <si>
-    <t>0.5079,0.1895,0.3117,0.0700</t>
-  </si>
-  <si>
-    <t>0.5997,0.2288,0.1615,0.0327</t>
-  </si>
-  <si>
-    <t>0.6518,0.2527,0.0586,0.0268</t>
-  </si>
-  <si>
-    <t>0.1477,0.8300,0.1238,0.0104</t>
-  </si>
-  <si>
-    <t>0.1577,0.8417,0.0955,0.0064</t>
-  </si>
-  <si>
-    <t>0.2833,0.6828,0.0554,0.0107</t>
-  </si>
-  <si>
-    <t>0.0222,0.9707,0.0542,0.0026</t>
-  </si>
-  <si>
-    <t>0.0141,0.9783,0.1002,0.0020</t>
-  </si>
-  <si>
-    <t>0.6186,0.2276,0.1738,0.0412</t>
-  </si>
-  <si>
-    <t>0.5456,0.2597,0.1477,0.0942</t>
-  </si>
-  <si>
-    <t>0.1685,0.1308,0.8306,0.0027</t>
-  </si>
-  <si>
-    <t>0.5674,0.2248,0.1816,0.0308</t>
-  </si>
-  <si>
-    <t>0.4983,0.1450,0.4031,0.0104</t>
-  </si>
-  <si>
-    <t>0.7550,0.0671,0.1686,0.0300</t>
-  </si>
-  <si>
-    <t>0.1621,0.1392,0.8109,0.0104</t>
-  </si>
-  <si>
-    <t>0.3096,0.7680,0.0373,0.0029</t>
-  </si>
-  <si>
-    <t>0.3259,0.5265,0.1611,0.0593</t>
-  </si>
-  <si>
-    <t>0.0044,0.8679,0.9512,0.0008</t>
-  </si>
-  <si>
-    <t>0.3264,0.6002,0.1671,0.0159</t>
-  </si>
-  <si>
-    <t>0.6748,0.1525,0.0378,0.0563</t>
-  </si>
-  <si>
-    <t>0.3445,0.5772,0.0745,0.0265</t>
-  </si>
-  <si>
-    <t>0.2718,0.7234,0.0671,0.0122</t>
-  </si>
-  <si>
-    <t>0.4070,0.5003,0.1393,0.0247</t>
-  </si>
-  <si>
-    <t>0.0455,0.8828,0.3005,0.0082</t>
-  </si>
-  <si>
-    <t>0.4649,0.2695,0.2673,0.0265</t>
-  </si>
-  <si>
-    <t>0.3076,0.2021,0.5342,0.0093</t>
-  </si>
-  <si>
-    <t>0.4316,0.2110,0.4116,0.0142</t>
-  </si>
-  <si>
-    <t>0.5761,0.1208,0.3433,0.0135</t>
-  </si>
-  <si>
-    <t>0.0544,0.9541,0.0445,0.0023</t>
-  </si>
-  <si>
-    <t>0.2001,0.3856,0.6329,0.0193</t>
-  </si>
-  <si>
-    <t>0.5464,0.3001,0.0623,0.0573</t>
-  </si>
-  <si>
-    <t>0.0551,0.9502,0.0523,0.0033</t>
-  </si>
-  <si>
-    <t>0.1903,0.7786,0.1593,0.0089</t>
-  </si>
-  <si>
-    <t>0.4383,0.5577,0.0464,0.0128</t>
-  </si>
-  <si>
-    <t>0.0080,0.9121,0.7084,0.0018</t>
-  </si>
-  <si>
-    <t>0.1747,0.4102,0.6589,0.0091</t>
-  </si>
-  <si>
-    <t>0.2880,0.3914,0.4417,0.0311</t>
-  </si>
-  <si>
-    <t>0.2988,0.0722,0.7264,0.0210</t>
-  </si>
-  <si>
-    <t>0.0049,0.5938,0.9749,0.0004</t>
-  </si>
-  <si>
-    <t>0.1037,0.3211,0.7213,0.0037</t>
-  </si>
-  <si>
-    <t>0.4812,0.5190,0.0371,0.0110</t>
-  </si>
-  <si>
-    <t>0.3566,0.6541,0.0521,0.0090</t>
-  </si>
-  <si>
-    <t>0.5832,0.3620,0.0534,0.0206</t>
-  </si>
-  <si>
-    <t>0.0379,0.7548,0.7742,0.0068</t>
-  </si>
-  <si>
-    <t>0.5567,0.3996,0.0441,0.0173</t>
-  </si>
-  <si>
-    <t>0.4401,0.4685,0.0488,0.0194</t>
-  </si>
-  <si>
-    <t>0.6393,0.3103,0.0623,0.0335</t>
-  </si>
-  <si>
-    <t>0.0252,0.9270,0.4773,0.0020</t>
-  </si>
-  <si>
-    <t>0.0551,0.4275,0.7871,0.0019</t>
-  </si>
-  <si>
-    <t>0.0650,0.8052,0.5418,0.0030</t>
-  </si>
-  <si>
-    <t>0.0067,0.9583,0.5751,0.0005</t>
-  </si>
-  <si>
-    <t>0.0241,0.5378,0.9135,0.0032</t>
-  </si>
-  <si>
-    <t>0.4959,0.4421,0.1051,0.0127</t>
-  </si>
-  <si>
-    <t>0.0079,0.9917,0.0285,0.0003</t>
-  </si>
-  <si>
-    <t>0.3981,0.5512,0.1216,0.0185</t>
-  </si>
-  <si>
-    <t>0.3882,0.5789,0.1014,0.0151</t>
-  </si>
-  <si>
-    <t>0.0041,0.7823,0.9616,0.0009</t>
-  </si>
-  <si>
-    <t>0.0365,0.7780,0.6852,0.0041</t>
-  </si>
-  <si>
-    <t>0.1176,0.7667,0.3860,0.0055</t>
-  </si>
-  <si>
-    <t>0.0100,0.9779,0.1498,0.0004</t>
-  </si>
-  <si>
-    <t>0.0112,0.9668,0.3408,0.0022</t>
-  </si>
-  <si>
-    <t>0.5377,0.2753,0.1542,0.0735</t>
-  </si>
-  <si>
-    <t>0.6609,0.1663,0.0332,0.0474</t>
-  </si>
-  <si>
-    <t>0.8631,0.0578,0.0075,0.0239</t>
-  </si>
-  <si>
-    <t>0.4496,0.4285,0.0961,0.0468</t>
-  </si>
-  <si>
-    <t>0.5968,0.1755,0.1121,0.1269</t>
-  </si>
-  <si>
-    <t>0.5582,0.1795,0.1135,0.1712</t>
-  </si>
-  <si>
-    <t>0.0252,0.6798,0.8356,0.0031</t>
-  </si>
-  <si>
-    <t>0.0113,0.7286,0.9222,0.0029</t>
-  </si>
-  <si>
-    <t>0.0564,0.6568,0.7177,0.0098</t>
-  </si>
-  <si>
-    <t>0.0579,0.6298,0.7637,0.0095</t>
-  </si>
-  <si>
-    <t>0.0284,0.9551,0.1946,0.0012</t>
-  </si>
-  <si>
-    <t>0.0389,0.7741,0.7165,0.0039</t>
-  </si>
-  <si>
-    <t>0.2941,0.6762,0.1317,0.0108</t>
-  </si>
-  <si>
-    <t>0.4498,0.5400,0.0344,0.0134</t>
-  </si>
-  <si>
-    <t>0.1130,0.8574,0.1217,0.0108</t>
-  </si>
-  <si>
-    <t>0.3582,0.6082,0.0971,0.0125</t>
-  </si>
-  <si>
-    <t>0.4753,0.4817,0.1120,0.0227</t>
-  </si>
-  <si>
-    <t>0.3730,0.6340,0.0821,0.0126</t>
-  </si>
-  <si>
-    <t>0.3303,0.5542,0.1509,0.0416</t>
-  </si>
-  <si>
-    <t>0.2868,0.6594,0.1809,0.0290</t>
-  </si>
-  <si>
-    <t>0.2708,0.6860,0.0968,0.0170</t>
-  </si>
-  <si>
-    <t>0.6886,0.2062,0.0287,0.0263</t>
-  </si>
-  <si>
-    <t>0.2924,0.7147,0.0589,0.0106</t>
-  </si>
-  <si>
-    <t>0.7352,0.1392,0.0218,0.0336</t>
-  </si>
-  <si>
-    <t>0.2473,0.6984,0.1582,0.0219</t>
-  </si>
-  <si>
-    <t>0.0817,0.9132,0.0948,0.0061</t>
-  </si>
-  <si>
-    <t>0.4339,0.4636,0.0393,0.0202</t>
-  </si>
-  <si>
-    <t>0.4051,0.5816,0.0371,0.0097</t>
-  </si>
-  <si>
-    <t>0.0537,0.4027,0.8916,0.0095</t>
-  </si>
-  <si>
-    <t>0.1444,0.2916,0.7249,0.0172</t>
-  </si>
-  <si>
-    <t>0.7507,0.1015,0.1302,0.0467</t>
-  </si>
-  <si>
-    <t>0.5299,0.3471,0.1896,0.0206</t>
-  </si>
-  <si>
-    <t>0.2223,0.8146,0.0478,0.0032</t>
-  </si>
-  <si>
-    <t>0.3135,0.6626,0.0848,0.0155</t>
-  </si>
-  <si>
-    <t>0.1882,0.8188,0.0726,0.0070</t>
-  </si>
-  <si>
-    <t>0.2968,0.6511,0.1079,0.0208</t>
-  </si>
-  <si>
-    <t>0.0292,0.9518,0.0997,0.0103</t>
-  </si>
-  <si>
-    <t>0.0096,0.9810,0.0988,0.0017</t>
-  </si>
-  <si>
-    <t>0.2702,0.7324,0.0570,0.0068</t>
-  </si>
-  <si>
-    <t>0.7355,0.1493,0.0269,0.0431</t>
-  </si>
-  <si>
-    <t>0.2394,0.1868,0.7087,0.0205</t>
-  </si>
-  <si>
-    <t>0.7089,0.2093,0.0820,0.0248</t>
-  </si>
-  <si>
-    <t>0.6280,0.2560,0.0986,0.0232</t>
-  </si>
-  <si>
-    <t>0.6021,0.1929,0.1131,0.1018</t>
-  </si>
-  <si>
-    <t>0.0652,0.9281,0.1257,0.0059</t>
-  </si>
-  <si>
-    <t>0.3261,0.6912,0.0529,0.0098</t>
-  </si>
-  <si>
-    <t>0.2740,0.6469,0.1319,0.0254</t>
-  </si>
-  <si>
-    <t>0.0236,0.9578,0.3016,0.0034</t>
-  </si>
-  <si>
-    <t>0.2480,0.7354,0.1149,0.0055</t>
-  </si>
-  <si>
-    <t>0.3932,0.5416,0.0706,0.0194</t>
-  </si>
-  <si>
-    <t>0.2026,0.7913,0.1483,0.0093</t>
-  </si>
-  <si>
-    <t>0.5561,0.3844,0.0712,0.0303</t>
-  </si>
-  <si>
-    <t>0.4111,0.5751,0.0978,0.0155</t>
-  </si>
-  <si>
-    <t>0.3718,0.5394,0.1125,0.0301</t>
-  </si>
-  <si>
-    <t>0.5694,0.3452,0.0666,0.0322</t>
-  </si>
-  <si>
-    <t>0.5516,0.3802,0.0502,0.0278</t>
-  </si>
-  <si>
-    <t>0.6985,0.2585,0.0413,0.0169</t>
-  </si>
-  <si>
-    <t>0.4493,0.5441,0.0867,0.0144</t>
-  </si>
-  <si>
-    <t>0.6151,0.3454,0.0398,0.0173</t>
-  </si>
-  <si>
-    <t>0.0466,0.7852,0.6795,0.0057</t>
-  </si>
-  <si>
-    <t>0.2466,0.3898,0.4416,0.0091</t>
-  </si>
-  <si>
-    <t>0.0812,0.3801,0.7410,0.0038</t>
-  </si>
-  <si>
-    <t>0.4907,0.0926,0.4147,0.0104</t>
-  </si>
-  <si>
-    <t>0.6727,0.1901,0.0976,0.0646</t>
-  </si>
-  <si>
-    <t>0.6697,0.2818,0.0471,0.0170</t>
-  </si>
-  <si>
-    <t>0.8668,0.0508,0.0709,0.0184</t>
-  </si>
-  <si>
-    <t>0.5996,0.2506,0.1106,0.0570</t>
-  </si>
-  <si>
-    <t>0.5492,0.3075,0.1074,0.0472</t>
-  </si>
-  <si>
-    <t>0.6475,0.1323,0.0204,0.0840</t>
-  </si>
-  <si>
-    <t>0.6283,0.2167,0.1057,0.0868</t>
-  </si>
-  <si>
-    <t>0.4579,0.1681,0.1341,0.2914</t>
-  </si>
-  <si>
-    <t>0.0311,0.9273,0.2682,0.0151</t>
-  </si>
-  <si>
-    <t>0.4204,0.6164,0.0683,0.0083</t>
-  </si>
-  <si>
-    <t>0.3789,0.6461,0.0319,0.0078</t>
-  </si>
-  <si>
-    <t>0.5630,0.3540,0.0547,0.0343</t>
-  </si>
-  <si>
-    <t>0.2616,0.6744,0.1226,0.0283</t>
-  </si>
-  <si>
-    <t>0.4221,0.5128,0.0829,0.0150</t>
-  </si>
-  <si>
-    <t>0.6140,0.2740,0.0489,0.0376</t>
-  </si>
-  <si>
-    <t>0.4286,0.6037,0.0366,0.0079</t>
-  </si>
-  <si>
-    <t>0.0274,0.7773,0.8345,0.0176</t>
-  </si>
-  <si>
-    <t>0.7190,0.2137,0.0359,0.0265</t>
-  </si>
-  <si>
-    <t>0.8020,0.1415,0.0188,0.0135</t>
-  </si>
-  <si>
-    <t>0.3587,0.5835,0.0749,0.0164</t>
-  </si>
-  <si>
-    <t>0.5607,0.4682,0.0370,0.0077</t>
-  </si>
-  <si>
-    <t>0.5871,0.3340,0.0798,0.0237</t>
-  </si>
-  <si>
-    <t>0.2869,0.6294,0.1541,0.0226</t>
-  </si>
-  <si>
-    <t>0.4739,0.4394,0.1188,0.0272</t>
-  </si>
-  <si>
-    <t>0.7427,0.1586,0.0303,0.0286</t>
-  </si>
-  <si>
-    <t>0.3819,0.5190,0.0604,0.0241</t>
-  </si>
-  <si>
-    <t>0.5645,0.3225,0.0975,0.0448</t>
-  </si>
-  <si>
-    <t>0.5413,0.4498,0.0577,0.0169</t>
-  </si>
-  <si>
-    <t>0.3025,0.5802,0.2284,0.0470</t>
-  </si>
-  <si>
-    <t>0.6528,0.3361,0.0371,0.0103</t>
-  </si>
-  <si>
-    <t>0.2808,0.6563,0.1016,0.0235</t>
-  </si>
-  <si>
-    <t>0.5193,0.5342,0.0490,0.0108</t>
-  </si>
-  <si>
-    <t>0.6766,0.2655,0.0364,0.0195</t>
-  </si>
-  <si>
-    <t>0.3373,0.5694,0.1500,0.0267</t>
-  </si>
-  <si>
-    <t>0.3047,0.6450,0.0543,0.0167</t>
-  </si>
-  <si>
-    <t>0.2702,0.7909,0.0379,0.0046</t>
-  </si>
-  <si>
-    <t>0.7748,0.1059,0.0181,0.0305</t>
-  </si>
-  <si>
-    <t>0.3122,0.6940,0.0496,0.0126</t>
-  </si>
-  <si>
-    <t>0.4117,0.4778,0.1104,0.0381</t>
-  </si>
-  <si>
-    <t>0.4876,0.4456,0.1086,0.0296</t>
-  </si>
-  <si>
-    <t>0.6574,0.3311,0.0344,0.0137</t>
-  </si>
-  <si>
-    <t>0.0039,0.7492,0.9638,0.0009</t>
-  </si>
-  <si>
-    <t>0.3028,0.6698,0.0968,0.0143</t>
-  </si>
-  <si>
-    <t>0.0499,0.2226,0.9034,0.0015</t>
-  </si>
-  <si>
-    <t>0.1337,0.2099,0.7991,0.0078</t>
-  </si>
-  <si>
-    <t>0.4335,0.0960,0.5793,0.0159</t>
-  </si>
-  <si>
-    <t>0.1070,0.5203,0.6548,0.0119</t>
-  </si>
-  <si>
-    <t>0.0741,0.1194,0.8713,0.0040</t>
-  </si>
-  <si>
-    <t>0.0705,0.1291,0.9028,0.0017</t>
-  </si>
-  <si>
-    <t>0.1901,0.4454,0.6306,0.0155</t>
-  </si>
-  <si>
-    <t>0.5227,0.3249,0.1555,0.0453</t>
-  </si>
-  <si>
-    <t>0.5748,0.2622,0.1626,0.0475</t>
-  </si>
-  <si>
-    <t>0.7689,0.1259,0.0433,0.0401</t>
-  </si>
-  <si>
-    <t>0.3868,0.5567,0.1213,0.0115</t>
-  </si>
-  <si>
-    <t>0.5338,0.3979,0.0993,0.0179</t>
-  </si>
-  <si>
-    <t>0.6444,0.1995,0.1291,0.0305</t>
-  </si>
-  <si>
-    <t>0.7156,0.2018,0.0420,0.0192</t>
-  </si>
-  <si>
-    <t>0.6138,0.2216,0.1299,0.0663</t>
-  </si>
-  <si>
-    <t>0.3837,0.5910,0.0755,0.0147</t>
-  </si>
-  <si>
-    <t>0.2221,0.8269,0.0513,0.0061</t>
-  </si>
-  <si>
-    <t>0.0615,0.9307,0.0414,0.0045</t>
-  </si>
-  <si>
-    <t>0.5117,0.5376,0.0405,0.0082</t>
-  </si>
-  <si>
-    <t>0.6317,0.3634,0.0543,0.0147</t>
-  </si>
-  <si>
-    <t>0.6253,0.2394,0.1324,0.0296</t>
-  </si>
-  <si>
-    <t>0.7881,0.0929,0.0651,0.0372</t>
-  </si>
-  <si>
-    <t>0.7847,0.0758,0.0664,0.0712</t>
-  </si>
-  <si>
-    <t>0.7072,0.1105,0.1591,0.0703</t>
-  </si>
-  <si>
-    <t>0.6286,0.2406,0.0593,0.0332</t>
-  </si>
-  <si>
-    <t>0.1769,0.3711,0.6785,0.0147</t>
-  </si>
-  <si>
-    <t>0.4725,0.2316,0.3199,0.0201</t>
-  </si>
-  <si>
-    <t>0.4403,0.4234,0.2514,0.0228</t>
-  </si>
-  <si>
-    <t>0.3166,0.3590,0.4020,0.0293</t>
-  </si>
-  <si>
-    <t>0.1005,0.6084,0.4925,0.0037</t>
-  </si>
-  <si>
-    <t>0.6206,0.3175,0.0433,0.0199</t>
-  </si>
-  <si>
-    <t>0.6799,0.1679,0.0238,0.0462</t>
-  </si>
-  <si>
-    <t>0.5732,0.3214,0.0397,0.0260</t>
-  </si>
-  <si>
-    <t>0.4308,0.5652,0.0611,0.0140</t>
-  </si>
-  <si>
-    <t>0.2748,0.7456,0.0690,0.0053</t>
-  </si>
-  <si>
-    <t>0.5594,0.4070,0.0389,0.0178</t>
-  </si>
-  <si>
-    <t>0.7662,0.2077,0.0216,0.0096</t>
-  </si>
-  <si>
-    <t>0.5259,0.3441,0.0594,0.0381</t>
-  </si>
-  <si>
-    <t>0.5778,0.2056,0.2323,0.0626</t>
-  </si>
-  <si>
-    <t>0.7206,0.1922,0.0432,0.0361</t>
-  </si>
-  <si>
-    <t>0.4467,0.5376,0.0700,0.0124</t>
-  </si>
-  <si>
-    <t>0.0471,0.5409,0.7851,0.0042</t>
-  </si>
-  <si>
-    <t>0.0551,0.3508,0.8706,0.0068</t>
-  </si>
-  <si>
-    <t>0.5162,0.2661,0.2661,0.0167</t>
-  </si>
-  <si>
-    <t>0.0215,0.1806,0.9691,0.0009</t>
-  </si>
-  <si>
-    <t>0.1570,0.3494,0.7216,0.0160</t>
-  </si>
-  <si>
-    <t>0.1717,0.1450,0.7578,0.0238</t>
-  </si>
-  <si>
-    <t>0.2135,0.0827,0.7129,0.0032</t>
-  </si>
-  <si>
-    <t>0.4621,0.2790,0.3305,0.0662</t>
-  </si>
-  <si>
-    <t>0.7432,0.1268,0.0711,0.0341</t>
-  </si>
-  <si>
-    <t>0.6761,0.0747,0.2607,0.0218</t>
-  </si>
-  <si>
-    <t>0.8158,0.0910,0.0304,0.0344</t>
-  </si>
-  <si>
-    <t>0.3659,0.5542,0.0826,0.0171</t>
-  </si>
-  <si>
-    <t>0.5962,0.3697,0.0545,0.0198</t>
-  </si>
-  <si>
-    <t>0.3104,0.7064,0.1035,0.0078</t>
-  </si>
-  <si>
-    <t>0.3531,0.6505,0.0631,0.0109</t>
-  </si>
-  <si>
-    <t>0.4610,0.5051,0.0464,0.0144</t>
-  </si>
-  <si>
-    <t>0.5038,0.4477,0.0642,0.0240</t>
-  </si>
-  <si>
-    <t>0.2961,0.7077,0.0967,0.0119</t>
-  </si>
-  <si>
-    <t>0.7655,0.2328,0.0170,0.0097</t>
-  </si>
-  <si>
-    <t>0.1871,0.7169,0.2587,0.0138</t>
-  </si>
-  <si>
-    <t>0.0253,0.8029,0.7171,0.0034</t>
-  </si>
-  <si>
-    <t>0.0232,0.7953,0.7998,0.0037</t>
-  </si>
-  <si>
-    <t>0.2630,0.2625,0.5568,0.0069</t>
-  </si>
-  <si>
-    <t>0.2711,0.2466,0.5917,0.0144</t>
-  </si>
-  <si>
-    <t>0.5518,0.1751,0.2525,0.0264</t>
-  </si>
-  <si>
-    <t>0.5281,0.3482,0.1593,0.0132</t>
-  </si>
-  <si>
-    <t>0.2726,0.4229,0.4601,0.0205</t>
-  </si>
-  <si>
-    <t>0.6748,0.2088,0.0533,0.0377</t>
-  </si>
-  <si>
-    <t>0.6632,0.0466,0.0284,0.2089</t>
-  </si>
-  <si>
-    <t>0.7455,0.1126,0.0399,0.0564</t>
-  </si>
-  <si>
-    <t>0.4897,0.2252,0.1208,0.1470</t>
-  </si>
-  <si>
-    <t>0.8131,0.0652,0.0269,0.0598</t>
-  </si>
-  <si>
-    <t>0.6642,0.2104,0.0505,0.0601</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9015,0.0308,0.0267,0.0317</t>
+  </si>
+  <si>
+    <t>0.0109,0.0015,0.0008,0.9956</t>
+  </si>
+  <si>
+    <t>0.8017,0.0039,0.0113,0.2481</t>
+  </si>
+  <si>
+    <t>0.0630,0.0151,0.0031,0.9671</t>
+  </si>
+  <si>
+    <t>0.9926,0.0045,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9938,0.0029,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0078,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0013,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9954,0.0023,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0096,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0038,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9924,0.0025,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.8447,0.0165,0.1701,0.0089</t>
+  </si>
+  <si>
+    <t>0.0368,0.0264,0.9572,0.0020</t>
+  </si>
+  <si>
+    <t>0.0858,0.0487,0.9203,0.0011</t>
+  </si>
+  <si>
+    <t>0.0108,0.0124,0.9733,0.0026</t>
+  </si>
+  <si>
+    <t>0.8286,0.0209,0.1768,0.0168</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9974,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0626,0.9101,0.0181,0.0109</t>
+  </si>
+  <si>
+    <t>0.0053,0.9877,0.0050,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.9977,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.6741,0.0015,0.3015,0.0178</t>
+  </si>
+  <si>
+    <t>0.1551,0.0215,0.8205,0.0187</t>
+  </si>
+  <si>
+    <t>0.0023,0.0015,0.9962,0.0007</t>
+  </si>
+  <si>
+    <t>0.0132,0.0136,0.9795,0.0028</t>
+  </si>
+  <si>
+    <t>0.0168,0.0024,0.9882,0.0004</t>
+  </si>
+  <si>
+    <t>0.0135,0.0094,0.9808,0.0013</t>
+  </si>
+  <si>
+    <t>0.0057,0.0032,0.9824,0.0154</t>
+  </si>
+  <si>
+    <t>0.7890,0.1767,0.0200,0.0005</t>
+  </si>
+  <si>
+    <t>0.0645,0.2101,0.8670,0.0113</t>
+  </si>
+  <si>
+    <t>0.0006,0.0118,0.9979,0.0008</t>
+  </si>
+  <si>
+    <t>0.0023,0.9801,0.1542,0.0005</t>
+  </si>
+  <si>
+    <t>0.8612,0.0803,0.0373,0.0303</t>
+  </si>
+  <si>
+    <t>0.2809,0.1323,0.5652,0.0161</t>
+  </si>
+  <si>
+    <t>0.7417,0.3701,0.0157,0.0015</t>
+  </si>
+  <si>
+    <t>0.0080,0.9716,0.1946,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.8020,0.5232,0.0032</t>
+  </si>
+  <si>
+    <t>0.0275,0.0060,0.9450,0.0247</t>
+  </si>
+  <si>
+    <t>0.0067,0.0088,0.9839,0.0049</t>
+  </si>
+  <si>
+    <t>0.0935,0.0031,0.9486,0.0018</t>
+  </si>
+  <si>
+    <t>0.0155,0.0378,0.9646,0.0092</t>
+  </si>
+  <si>
+    <t>0.0041,0.9924,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.0149,0.0085,0.9683,0.0135</t>
+  </si>
+  <si>
+    <t>0.0050,0.7427,0.0092,0.9415</t>
+  </si>
+  <si>
+    <t>0.0009,0.9966,0.0087,0.0028</t>
+  </si>
+  <si>
+    <t>0.0008,0.9955,0.0130,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0063,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.0107,0.9957,0.0014</t>
+  </si>
+  <si>
+    <t>0.0054,0.3920,0.9618,0.0023</t>
+  </si>
+  <si>
+    <t>0.0169,0.0090,0.9748,0.0031</t>
+  </si>
+  <si>
+    <t>0.0132,0.0026,0.9837,0.0056</t>
+  </si>
+  <si>
+    <t>0.0017,0.0042,0.9947,0.0032</t>
+  </si>
+  <si>
+    <t>0.0075,0.7629,0.8761,0.0028</t>
+  </si>
+  <si>
+    <t>0.9824,0.0224,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9897,0.0054,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.9776,0.0080,0.0085,0.0041</t>
+  </si>
+  <si>
+    <t>0.0050,0.0298,0.9914,0.0018</t>
+  </si>
+  <si>
+    <t>0.9888,0.0056,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9931,0.0060,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9700,0.0163,0.0079,0.0043</t>
+  </si>
+  <si>
+    <t>0.0001,0.9473,0.9917,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0880,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0013,0.9974,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.9633,0.9436,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.9984,0.0009</t>
+  </si>
+  <si>
+    <t>0.0221,0.9508,0.0283,0.0011</t>
+  </si>
+  <si>
+    <t>0.0033,0.9949,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.7581,0.0235,0.3426,0.0063</t>
+  </si>
+  <si>
+    <t>0.0184,0.1767,0.9480,0.0160</t>
+  </si>
+  <si>
+    <t>0.0039,0.0126,0.9944,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9361,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.7530,0.9426,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.9966,0.1403,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9759,0.8712,0.0005</t>
+  </si>
+  <si>
+    <t>0.0076,0.0019,0.0310,0.9823</t>
+  </si>
+  <si>
+    <t>0.0013,0.0008,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.0029,0.0245,0.0024,0.9956</t>
+  </si>
+  <si>
+    <t>0.0035,0.0028,0.0290,0.9872</t>
+  </si>
+  <si>
+    <t>0.0145,0.0018,0.0032,0.9911</t>
+  </si>
+  <si>
+    <t>0.0025,0.0069,0.0059,0.9956</t>
+  </si>
+  <si>
+    <t>0.0007,0.9804,0.7774,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.8689,0.9676,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.8178,0.9654,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.4799,0.9448,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.8700,0.9728,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.9639,0.7144,0.0021</t>
+  </si>
+  <si>
+    <t>0.9942,0.0042,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9906,0.0125,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9499,0.0751,0.0033,0.0018</t>
+  </si>
+  <si>
+    <t>0.9776,0.0104,0.0039,0.0048</t>
+  </si>
+  <si>
+    <t>0.9811,0.0172,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9868,0.0083,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.9916,0.0046,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9883,0.0094,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0030,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9862,0.0082,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.9968,0.0017,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0014,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9874,0.0123,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0018,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9971,0.0007,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.0022,0.0014,0.9937,0.0047</t>
+  </si>
+  <si>
+    <t>0.0158,0.0013,0.9858,0.0011</t>
+  </si>
+  <si>
+    <t>0.9834,0.0011,0.0193,0.0003</t>
+  </si>
+  <si>
+    <t>0.0059,0.0009,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.9919,0.0034,0.0007</t>
+  </si>
+  <si>
+    <t>0.0087,0.9875,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.9851,0.0049,0.0017</t>
+  </si>
+  <si>
+    <t>0.0802,0.9152,0.0268,0.0072</t>
+  </si>
+  <si>
+    <t>0.0016,0.9970,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9984,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.6376,0.4614,0.0137,0.0020</t>
+  </si>
+  <si>
+    <t>0.6542,0.1583,0.1604,0.0465</t>
+  </si>
+  <si>
+    <t>0.1349,0.0111,0.9051,0.0036</t>
+  </si>
+  <si>
+    <t>0.2478,0.0594,0.6886,0.0052</t>
+  </si>
+  <si>
+    <t>0.2941,0.0340,0.6643,0.0318</t>
+  </si>
+  <si>
+    <t>0.0118,0.7353,0.0364,0.7711</t>
+  </si>
+  <si>
+    <t>0.0007,0.9964,0.0080,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.9961,0.0095,0.0067</t>
+  </si>
+  <si>
+    <t>0.0002,0.9976,0.0065,0.0045</t>
+  </si>
+  <si>
+    <t>0.0002,0.9870,0.9342,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.9924,0.0204,0.0000</t>
+  </si>
+  <si>
+    <t>0.0679,0.9401,0.0162,0.0012</t>
+  </si>
+  <si>
+    <t>0.8143,0.2759,0.0118,0.0037</t>
+  </si>
+  <si>
+    <t>0.9851,0.0098,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9908,0.0046,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9901,0.0038,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.9763,0.0096,0.0068,0.0040</t>
+  </si>
+  <si>
+    <t>0.9935,0.0025,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9845,0.0070,0.0028,0.0022</t>
+  </si>
+  <si>
+    <t>0.9789,0.0061,0.0106,0.0041</t>
+  </si>
+  <si>
+    <t>0.9909,0.0037,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.0011,0.0251,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.8543,0.8843,0.0004</t>
+  </si>
+  <si>
+    <t>0.0059,0.0167,0.9896,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.0066,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.8519,0.0237,0.0981,0.0166</t>
+  </si>
+  <si>
+    <t>0.4279,0.0141,0.7009,0.0056</t>
+  </si>
+  <si>
+    <t>0.3684,0.0048,0.7802,0.0032</t>
+  </si>
+  <si>
+    <t>0.6199,0.0619,0.3884,0.0338</t>
+  </si>
+  <si>
+    <t>0.0801,0.0056,0.0108,0.9575</t>
+  </si>
+  <si>
+    <t>0.0004,0.0026,0.0040,0.9982</t>
+  </si>
+  <si>
+    <t>0.0009,0.0128,0.0011,0.9986</t>
+  </si>
+  <si>
+    <t>0.0216,0.0012,0.0088,0.9821</t>
+  </si>
+  <si>
+    <t>0.0010,0.9313,0.9337,0.0015</t>
+  </si>
+  <si>
+    <t>0.9834,0.0093,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.1016,0.8778,0.0102,0.0224</t>
+  </si>
+  <si>
+    <t>0.9927,0.0024,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.4525,0.6258,0.0231,0.0115</t>
+  </si>
+  <si>
+    <t>0.9667,0.0070,0.0065,0.0208</t>
+  </si>
+  <si>
+    <t>0.6845,0.0494,0.0115,0.2521</t>
+  </si>
+  <si>
+    <t>0.9841,0.0048,0.0025,0.0060</t>
+  </si>
+  <si>
+    <t>0.0011,0.5107,0.9871,0.0016</t>
+  </si>
+  <si>
+    <t>0.5672,0.0017,0.0041,0.6729</t>
+  </si>
+  <si>
+    <t>0.7868,0.0568,0.0341,0.1782</t>
+  </si>
+  <si>
+    <t>0.3680,0.6732,0.0266,0.0217</t>
+  </si>
+  <si>
+    <t>0.9740,0.0163,0.0066,0.0015</t>
+  </si>
+  <si>
+    <t>0.9690,0.0127,0.0142,0.0021</t>
+  </si>
+  <si>
+    <t>0.0961,0.8823,0.0382,0.0100</t>
+  </si>
+  <si>
+    <t>0.7468,0.0982,0.1528,0.0035</t>
+  </si>
+  <si>
+    <t>0.7149,0.3042,0.0345,0.0098</t>
+  </si>
+  <si>
+    <t>0.9876,0.0027,0.0022,0.0051</t>
+  </si>
+  <si>
+    <t>0.9910,0.0028,0.0014,0.0021</t>
+  </si>
+  <si>
+    <t>0.9718,0.0240,0.0071,0.0019</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9823,0.0072,0.0058,0.0022</t>
+  </si>
+  <si>
+    <t>0.9931,0.0030,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9828,0.0047,0.0077,0.0029</t>
+  </si>
+  <si>
+    <t>0.3814,0.7489,0.0048,0.0014</t>
+  </si>
+  <si>
+    <t>0.8256,0.2410,0.0171,0.0038</t>
+  </si>
+  <si>
+    <t>0.4143,0.6685,0.0232,0.0020</t>
+  </si>
+  <si>
+    <t>0.0300,0.4277,0.9231,0.0040</t>
+  </si>
+  <si>
+    <t>0.9471,0.0932,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9394,0.0747,0.0070,0.0018</t>
+  </si>
+  <si>
+    <t>0.9590,0.0671,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.9653,0.0382,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.0503,0.9975,0.0008</t>
+  </si>
+  <si>
+    <t>0.9484,0.0358,0.0183,0.0025</t>
+  </si>
+  <si>
+    <t>0.0030,0.0022,0.9955,0.0009</t>
+  </si>
+  <si>
+    <t>0.0021,0.0044,0.9956,0.0013</t>
+  </si>
+  <si>
+    <t>0.0071,0.0028,0.9898,0.0011</t>
+  </si>
+  <si>
+    <t>0.0092,0.0183,0.9857,0.0007</t>
+  </si>
+  <si>
+    <t>0.0038,0.0036,0.9952,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0035,0.9962,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.0025,0.9938,0.0025</t>
+  </si>
+  <si>
+    <t>0.0305,0.0112,0.9496,0.0020</t>
+  </si>
+  <si>
+    <t>0.0370,0.0098,0.9606,0.0019</t>
+  </si>
+  <si>
+    <t>0.1323,0.1684,0.7464,0.0089</t>
+  </si>
+  <si>
+    <t>0.1502,0.2110,0.6106,0.0052</t>
+  </si>
+  <si>
+    <t>0.2515,0.2360,0.6429,0.0160</t>
+  </si>
+  <si>
+    <t>0.8890,0.0351,0.0565,0.0014</t>
+  </si>
+  <si>
+    <t>0.3821,0.0395,0.5809,0.0515</t>
+  </si>
+  <si>
+    <t>0.1893,0.0876,0.6694,0.0668</t>
+  </si>
+  <si>
+    <t>0.1254,0.9200,0.0024,0.0009</t>
+  </si>
+  <si>
+    <t>0.1905,0.8305,0.0130,0.0009</t>
+  </si>
+  <si>
+    <t>0.7049,0.4328,0.0057,0.0019</t>
+  </si>
+  <si>
+    <t>0.9140,0.1835,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9565,0.0867,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.4433,0.4175,0.1168,0.0102</t>
+  </si>
+  <si>
+    <t>0.9015,0.0052,0.1565,0.0020</t>
+  </si>
+  <si>
+    <t>0.6612,0.0180,0.2797,0.0640</t>
+  </si>
+  <si>
+    <t>0.5146,0.0857,0.4628,0.0370</t>
+  </si>
+  <si>
+    <t>0.8089,0.0097,0.2639,0.0058</t>
+  </si>
+  <si>
+    <t>0.0029,0.0080,0.9914,0.0033</t>
+  </si>
+  <si>
+    <t>0.0107,0.0217,0.9787,0.0053</t>
+  </si>
+  <si>
+    <t>0.0256,0.0324,0.9470,0.0133</t>
+  </si>
+  <si>
+    <t>0.0268,0.0168,0.9522,0.0021</t>
+  </si>
+  <si>
+    <t>0.0038,0.4824,0.9310,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0020,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9743,0.0252,0.0057,0.0021</t>
+  </si>
+  <si>
+    <t>0.9875,0.0112,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9923,0.0092,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9721,0.0231,0.0011,0.0031</t>
+  </si>
+  <si>
+    <t>0.9871,0.0125,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9886,0.0041,0.0010,0.0029</t>
+  </si>
+  <si>
+    <t>0.9922,0.0062,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0154,0.0667,0.9717,0.0032</t>
+  </si>
+  <si>
+    <t>0.2170,0.3778,0.5952,0.0256</t>
+  </si>
+  <si>
+    <t>0.5638,0.0534,0.3303,0.1363</t>
+  </si>
+  <si>
+    <t>0.0021,0.0086,0.9950,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0116,0.9944,0.0057</t>
+  </si>
+  <si>
+    <t>0.0134,0.0463,0.9622,0.0037</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.0055,0.9892,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.0016,0.9982,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.0075,0.9940,0.0007</t>
+  </si>
+  <si>
+    <t>0.0188,0.0519,0.9370,0.0067</t>
+  </si>
+  <si>
+    <t>0.6790,0.0413,0.2905,0.0350</t>
+  </si>
+  <si>
+    <t>0.6046,0.0016,0.6084,0.0019</t>
+  </si>
+  <si>
+    <t>0.9580,0.0062,0.0155,0.0104</t>
+  </si>
+  <si>
+    <t>0.9828,0.0194,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9896,0.0046,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.9824,0.0147,0.0033,0.0013</t>
+  </si>
+  <si>
+    <t>0.9941,0.0018,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9941,0.0025,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9828,0.0194,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0052,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9898,0.0041,0.0006,0.0023</t>
+  </si>
+  <si>
+    <t>0.0077,0.0108,0.9868,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0068,0.9945,0.0018</t>
+  </si>
+  <si>
+    <t>0.0046,0.0403,0.9843,0.0039</t>
+  </si>
+  <si>
+    <t>0.0318,0.0698,0.8955,0.0076</t>
+  </si>
+  <si>
+    <t>0.0039,0.0012,0.9939,0.0014</t>
+  </si>
+  <si>
+    <t>0.1434,0.0112,0.8787,0.0124</t>
+  </si>
+  <si>
+    <t>0.0351,0.1457,0.8731,0.0360</t>
+  </si>
+  <si>
+    <t>0.0272,0.0088,0.9306,0.0422</t>
+  </si>
+  <si>
+    <t>0.8520,0.0062,0.0022,0.1942</t>
+  </si>
+  <si>
+    <t>0.0101,0.0028,0.0012,0.9950</t>
+  </si>
+  <si>
+    <t>0.0124,0.0007,0.0113,0.9863</t>
+  </si>
+  <si>
+    <t>0.0038,0.0001,0.0006,0.9980</t>
+  </si>
+  <si>
+    <t>0.0020,0.0005,0.0010,0.9982</t>
+  </si>
+  <si>
+    <t>0.8848,0.0036,0.0014,0.1679</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,10 +2068,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,10 +2082,10 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,10 +2096,10 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2432,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2712,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,10 +2726,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,10 +2866,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2908,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,10 +3174,10 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,10 +3188,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,10 +3202,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,10 +3216,10 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,10 +3244,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,10 +3258,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,10 +3272,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,10 +3286,10 @@
         <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,10 +3314,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,10 +3342,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,10 +3356,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,10 +3384,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,10 +3734,10 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,10 +3748,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,10 +3804,10 @@
         <v>259</v>
       </c>
       <c r="C134" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,10 +4014,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,10 +4098,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>263</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,10 +4238,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,10 +4280,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,10 +4308,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,10 +4322,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4476,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,10 +4966,10 @@
         <v>259</v>
       </c>
       <c r="C217" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5050,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,10 +5218,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,10 +5246,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,10 +5260,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,10 +5274,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,10 +5302,10 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
